--- a/раунд_2.xlsx
+++ b/раунд_2.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H68"/>
+  <dimension ref="A1:H97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -630,126 +630,126 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>86194</v>
+        <v>131171</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>64372</v>
+        <v>120123</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H9" s="3" t="n">
-        <v>0.667</v>
+      <c r="H9" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>117080</v>
+        <v>86194</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>3</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>59618</v>
+        <v>64372</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H11" s="2" t="n">
-        <v>0</v>
+      <c r="H11" s="3" t="n">
+        <v>0.667</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>118534</v>
+        <v>117080</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>0</v>
@@ -760,19 +760,19 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>61605</v>
+        <v>59618</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>0</v>
@@ -786,19 +786,19 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>80299</v>
+        <v>118534</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>0</v>
@@ -807,122 +807,122 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B15" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="B15" s="2" t="n">
-        <v>39</v>
-      </c>
       <c r="C15" s="2" t="n">
-        <v>82060</v>
+        <v>61605</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H15" s="3" t="n">
-        <v>0.167</v>
+      <c r="H15" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>103407</v>
+        <v>107642</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.167</v>
+        <v>0.333</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>179751</v>
+        <v>80299</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H17" s="3" t="n">
-        <v>0.25</v>
+      <c r="H17" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>99935</v>
+        <v>109763</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H18" s="3" t="n">
-        <v>0.8</v>
+      <c r="H18" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>105958</v>
+        <v>82060</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>0</v>
@@ -931,163 +931,163 @@
         <v>8</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H19" s="2" t="n">
-        <v>1</v>
+      <c r="H19" s="3" t="n">
+        <v>0.167</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>69346</v>
+        <v>103407</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H20" s="2" t="n">
-        <v>1</v>
+      <c r="H20" s="3" t="n">
+        <v>0.167</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>84926</v>
+        <v>69822</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>101874</v>
+        <v>179751</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E22" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F22" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F22" s="2" t="n">
-        <v>25</v>
-      </c>
       <c r="G22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>109074</v>
+        <v>99935</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.375</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="B24" s="2" t="n">
         <v>49</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>124864</v>
+        <v>105958</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H24" s="3" t="n">
-        <v>0.889</v>
+      <c r="H24" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>89419</v>
+        <v>69346</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>0</v>
@@ -1098,13 +1098,13 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>169810</v>
+        <v>84926</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>0</v>
@@ -1113,50 +1113,50 @@
         <v>4</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>82786</v>
+        <v>101874</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H27" s="2" t="n">
-        <v>1</v>
+      <c r="H27" s="3" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>68176</v>
+        <v>90356</v>
       </c>
       <c r="D28" s="2" t="n">
         <v>0</v>
@@ -1165,111 +1165,111 @@
         <v>5</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>86029</v>
+        <v>109074</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="G29" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H29" s="2" t="n">
-        <v>1</v>
+      <c r="H29" s="3" t="n">
+        <v>0.375</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>52844</v>
+        <v>124864</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H30" s="2" t="n">
-        <v>0</v>
+      <c r="H30" s="3" t="n">
+        <v>0.889</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>141047</v>
+        <v>89419</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>29</v>
+        <v>61</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>86309</v>
+        <v>169810</v>
       </c>
       <c r="D32" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>0</v>
@@ -1280,74 +1280,74 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="B33" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>113701</v>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F33" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="C33" s="2" t="n">
-        <v>79877</v>
-      </c>
-      <c r="D33" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E33" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="F33" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="G33" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>66921</v>
+        <v>59029</v>
       </c>
       <c r="D34" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="G34" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H34" s="3" t="n">
-        <v>0.25</v>
+      <c r="H34" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="C35" s="2" t="n">
-        <v>134500</v>
+        <v>82786</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="G35" s="2" t="n">
         <v>0</v>
@@ -1358,19 +1358,19 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C36" s="2" t="n">
-        <v>151797</v>
+        <v>68176</v>
       </c>
       <c r="D36" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F36" s="2" t="n">
         <v>0</v>
@@ -1384,48 +1384,48 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C37" s="2" t="n">
-        <v>67576</v>
+        <v>86029</v>
       </c>
       <c r="D37" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G37" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H37" s="3" t="n">
-        <v>0.75</v>
+      <c r="H37" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C38" s="2" t="n">
-        <v>124100</v>
+        <v>62486</v>
       </c>
       <c r="D38" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G38" s="2" t="n">
         <v>0</v>
@@ -1436,39 +1436,39 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="C39" s="2" t="n">
-        <v>163877</v>
+        <v>49397</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G39" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="B40" s="2" t="n">
         <v>26</v>
       </c>
       <c r="C40" s="2" t="n">
-        <v>84274</v>
+        <v>80454</v>
       </c>
       <c r="D40" s="2" t="n">
         <v>0</v>
@@ -1482,106 +1482,106 @@
       <c r="G40" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H40" s="2" t="n">
-        <v>0</v>
+      <c r="H40" s="3" t="n">
+        <v>0.333</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C41" s="2" t="n">
-        <v>131607</v>
+        <v>52844</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="G41" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H41" s="3" t="n">
-        <v>0.8</v>
+      <c r="H41" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C42" s="2" t="n">
-        <v>94635</v>
+        <v>112092</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E42" s="2" t="n">
         <v>4</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G42" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C43" s="2" t="n">
-        <v>110924</v>
+        <v>141047</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G43" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="C44" s="2" t="n">
-        <v>101596</v>
+        <v>86309</v>
       </c>
       <c r="D44" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="G44" s="2" t="n">
         <v>0</v>
@@ -1592,22 +1592,22 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="B45" s="2" t="n">
         <v>29</v>
       </c>
       <c r="C45" s="2" t="n">
-        <v>64358</v>
+        <v>79877</v>
       </c>
       <c r="D45" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G45" s="2" t="n">
         <v>0</v>
@@ -1618,48 +1618,48 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="B46" s="2" t="n">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="C46" s="2" t="n">
-        <v>124186</v>
+        <v>66921</v>
       </c>
       <c r="D46" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G46" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H46" s="2" t="n">
-        <v>1</v>
+      <c r="H46" s="3" t="n">
+        <v>0.25</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="C47" s="2" t="n">
-        <v>131709</v>
+        <v>134500</v>
       </c>
       <c r="D47" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="G47" s="2" t="n">
         <v>0</v>
@@ -1670,45 +1670,45 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C48" s="2" t="n">
-        <v>107695</v>
+        <v>151797</v>
       </c>
       <c r="D48" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G48" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H48" s="3" t="n">
-        <v>0.75</v>
+      <c r="H48" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="C49" s="2" t="n">
-        <v>107475</v>
+        <v>67576</v>
       </c>
       <c r="D49" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F49" s="2" t="n">
         <v>0</v>
@@ -1716,77 +1716,77 @@
       <c r="G49" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H49" s="2" t="n">
-        <v>0</v>
+      <c r="H49" s="3" t="n">
+        <v>0.75</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C50" s="2" t="n">
-        <v>100649</v>
+        <v>124100</v>
       </c>
       <c r="D50" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G50" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C51" s="2" t="n">
-        <v>109028</v>
+        <v>115521</v>
       </c>
       <c r="D51" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G51" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H51" s="3" t="n">
-        <v>0.286</v>
+      <c r="H51" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="B52" s="2" t="n">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="C52" s="2" t="n">
-        <v>100589</v>
+        <v>163877</v>
       </c>
       <c r="D52" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F52" s="2" t="n">
         <v>0</v>
@@ -1795,27 +1795,27 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C53" s="2" t="n">
-        <v>75687</v>
+        <v>84274</v>
       </c>
       <c r="D53" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E53" s="2" t="n">
         <v>4</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="G53" s="2" t="n">
         <v>0</v>
@@ -1826,117 +1826,117 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>85</v>
+        <v>62</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="C54" s="2" t="n">
-        <v>125598</v>
+        <v>131607</v>
       </c>
       <c r="D54" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E54" s="2" t="n">
         <v>4</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G54" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H54" s="2" t="n">
-        <v>0</v>
+      <c r="H54" s="3" t="n">
+        <v>0.8</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="B55" s="2" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="C55" s="2" t="n">
-        <v>63799</v>
+        <v>94635</v>
       </c>
       <c r="D55" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E55" s="2" t="n">
         <v>4</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G55" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H55" s="3" t="n">
-        <v>0.5</v>
+      <c r="H55" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>91</v>
+        <v>65</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="C56" s="2" t="n">
-        <v>86616</v>
+        <v>110924</v>
       </c>
       <c r="D56" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G56" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="B57" s="2" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="C57" s="2" t="n">
-        <v>110992</v>
+        <v>101596</v>
       </c>
       <c r="D57" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G57" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H57" s="3" t="n">
-        <v>0.8</v>
+      <c r="H57" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="B58" s="2" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C58" s="2" t="n">
-        <v>88913</v>
+        <v>64358</v>
       </c>
       <c r="D58" s="2" t="n">
         <v>1</v>
@@ -1945,108 +1945,108 @@
         <v>4</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="G58" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>97</v>
+        <v>68</v>
       </c>
       <c r="B59" s="2" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="C59" s="2" t="n">
-        <v>89143</v>
+        <v>124186</v>
       </c>
       <c r="D59" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G59" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H59" s="3" t="n">
-        <v>0.333</v>
+      <c r="H59" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>101</v>
+        <v>71</v>
       </c>
       <c r="B60" s="2" t="n">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="C60" s="2" t="n">
-        <v>122978</v>
+        <v>131709</v>
       </c>
       <c r="D60" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G60" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>102</v>
+        <v>73</v>
       </c>
       <c r="B61" s="2" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C61" s="2" t="n">
-        <v>86817</v>
+        <v>107695</v>
       </c>
       <c r="D61" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G61" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H61" s="2" t="n">
-        <v>0</v>
+      <c r="H61" s="3" t="n">
+        <v>0.75</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="B62" s="2" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="C62" s="2" t="n">
-        <v>59520</v>
+        <v>107475</v>
       </c>
       <c r="D62" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F62" s="2" t="n">
         <v>0</v>
@@ -2060,13 +2060,13 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>104</v>
+        <v>75</v>
       </c>
       <c r="B63" s="2" t="n">
         <v>33</v>
       </c>
       <c r="C63" s="2" t="n">
-        <v>131047</v>
+        <v>123300</v>
       </c>
       <c r="D63" s="2" t="n">
         <v>1</v>
@@ -2086,74 +2086,74 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>107</v>
+        <v>76</v>
       </c>
       <c r="B64" s="2" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C64" s="2" t="n">
-        <v>107185</v>
+        <v>100649</v>
       </c>
       <c r="D64" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G64" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H64" s="3" t="n">
-        <v>0.2</v>
+      <c r="H64" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="B65" s="2" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C65" s="2" t="n">
-        <v>85370</v>
+        <v>65037</v>
       </c>
       <c r="D65" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G65" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H65" s="3" t="n">
-        <v>0.25</v>
+      <c r="H65" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>111</v>
+        <v>78</v>
       </c>
       <c r="B66" s="2" t="n">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="C66" s="2" t="n">
-        <v>95599</v>
+        <v>185203</v>
       </c>
       <c r="D66" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G66" s="2" t="n">
         <v>0</v>
@@ -2164,53 +2164,807 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="B67" s="2" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="C67" s="2" t="n">
-        <v>80514</v>
+        <v>109028</v>
       </c>
       <c r="D67" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G67" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H67" s="2" t="n">
-        <v>1</v>
+      <c r="H67" s="3" t="n">
+        <v>0.286</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="B68" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="C68" s="2" t="n">
+        <v>100589</v>
+      </c>
+      <c r="D68" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E68" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="B69" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="C69" s="2" t="n">
+        <v>121031</v>
+      </c>
+      <c r="D69" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E69" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F69" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="B70" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v>125690</v>
+      </c>
+      <c r="D70" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E70" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F70" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="G70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" s="3" t="n">
+        <v>0.833</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="B71" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v>75687</v>
+      </c>
+      <c r="D71" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E71" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F71" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="B72" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="C72" s="2" t="n">
+        <v>67677</v>
+      </c>
+      <c r="D72" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" s="3" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="B73" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="C73" s="2" t="n">
+        <v>125598</v>
+      </c>
+      <c r="D73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>86</v>
+      </c>
+      <c r="B74" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="C74" s="2" t="n">
+        <v>63799</v>
+      </c>
+      <c r="D74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F74" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" s="3" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="B75" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="C75" s="2" t="n">
+        <v>105312</v>
+      </c>
+      <c r="D75" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>89</v>
+      </c>
+      <c r="B76" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="C76" s="2" t="n">
+        <v>61323</v>
+      </c>
+      <c r="D76" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E76" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="B77" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="C77" s="2" t="n">
+        <v>72360</v>
+      </c>
+      <c r="D77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="B78" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="C78" s="2" t="n">
+        <v>86616</v>
+      </c>
+      <c r="D78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F78" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>92</v>
+      </c>
+      <c r="B79" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="C79" s="2" t="n">
+        <v>69506</v>
+      </c>
+      <c r="D79" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E79" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F79" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" s="3" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="B80" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="C80" s="2" t="n">
+        <v>110992</v>
+      </c>
+      <c r="D80" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" s="3" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>94</v>
+      </c>
+      <c r="B81" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="C81" s="2" t="n">
+        <v>117362</v>
+      </c>
+      <c r="D81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F81" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="B82" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="C82" s="2" t="n">
+        <v>88913</v>
+      </c>
+      <c r="D82" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E82" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F82" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="B83" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="C83" s="2" t="n">
+        <v>89143</v>
+      </c>
+      <c r="D83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F83" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" s="3" t="n">
+        <v>0.333</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>101</v>
+      </c>
+      <c r="B84" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="C84" s="2" t="n">
+        <v>122978</v>
+      </c>
+      <c r="D84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>102</v>
+      </c>
+      <c r="B85" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="C85" s="2" t="n">
+        <v>86817</v>
+      </c>
+      <c r="D85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>103</v>
+      </c>
+      <c r="B86" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="C86" s="2" t="n">
+        <v>59520</v>
+      </c>
+      <c r="D86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>104</v>
+      </c>
+      <c r="B87" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="C87" s="2" t="n">
+        <v>131047</v>
+      </c>
+      <c r="D87" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E87" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F87" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>105</v>
+      </c>
+      <c r="B88" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="C88" s="2" t="n">
+        <v>63562</v>
+      </c>
+      <c r="D88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E88" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>105</v>
+      </c>
+      <c r="B89" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="C89" s="2" t="n">
+        <v>103782</v>
+      </c>
+      <c r="D89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F89" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="G89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>107</v>
+      </c>
+      <c r="B90" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="C90" s="2" t="n">
+        <v>107185</v>
+      </c>
+      <c r="D90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E90" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F90" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="G90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" s="3" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>108</v>
+      </c>
+      <c r="B91" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="C91" s="2" t="n">
+        <v>108365</v>
+      </c>
+      <c r="D91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F91" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="G91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3" t="n">
+        <v>0.167</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>109</v>
+      </c>
+      <c r="B92" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="C92" s="2" t="n">
+        <v>85370</v>
+      </c>
+      <c r="D92" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E92" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F92" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="G92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" s="3" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="B93" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="C93" s="2" t="n">
+        <v>171884</v>
+      </c>
+      <c r="D93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F93" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>111</v>
+      </c>
+      <c r="B94" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="C94" s="2" t="n">
+        <v>95599</v>
+      </c>
+      <c r="D94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>112</v>
+      </c>
+      <c r="B95" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="C95" s="2" t="n">
+        <v>95484</v>
+      </c>
+      <c r="D95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F95" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="G95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>113</v>
+      </c>
+      <c r="B96" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="C96" s="2" t="n">
+        <v>80514</v>
+      </c>
+      <c r="D96" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E96" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="F96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n">
         <v>114</v>
       </c>
-      <c r="B68" s="2" t="n">
+      <c r="B97" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="C68" s="2" t="n">
+      <c r="C97" s="2" t="n">
         <v>131997</v>
       </c>
-      <c r="D68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E68" s="2" t="n">
+      <c r="D97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H68" s="2" t="n">
+      <c r="F97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" s="2" t="n">
         <v>0</v>
       </c>
     </row>
